--- a/etf_holdings/2026-09-03_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-03_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,7 +469,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00980A(103,105)、00985A(111,036)、00993A(93,191)</t>
+          <t>00980A(103,105)、00985A(111,036)、00407A(386,644)、00993A(93,191)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -541,12 +541,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -554,29 +554,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00993A(85,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00981A(-1,238,000)</t>
+          <t>00407A(-1,045,000)、00993A(-62,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -584,29 +584,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00982A(300,000)、00993A(328,000)</t>
+          <t>00993A(85,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00981A(-1,238,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -614,29 +614,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00981A(30,000)</t>
+          <t>00407A(25,000)、00993A(12,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>00993A(-6,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,17 +644,107 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>00982A(300,000)、00993A(328,000)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>混合</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>00981A(30,000)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>00993A(-6,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>00993A(219,000)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>00403A(全數賣出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00407A(130,000)、00993A(40,000)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-09-03_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-03_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,7 +469,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00980A(103,105)、00985A(111,036)、00407A(386,644)、00993A(93,191)</t>
+          <t>00980A(103,105)、00407A(386,644)、00993A(93,191)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,12 +511,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -534,19 +534,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00992A(-30,000)、00993A(-2,000)</t>
+          <t>00407A(-1,045,000)、00993A(-62,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -554,29 +554,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(85,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00407A(-1,045,000)、00993A(-62,000)</t>
+          <t>00981A(-1,238,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -584,17 +584,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00993A(85,000)</t>
+          <t>00990A(657,000)、00993A(72,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>00981A(-1,238,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,29 +644,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00982A(300,000)、00993A(328,000)</t>
+          <t>00990A(新納入)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(-27,000)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -674,29 +674,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00981A(30,000)</t>
+          <t>00982A(300,000)、00993A(328,000)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>00993A(-6,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -709,40 +709,100 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>00993A(219,000)</t>
+          <t>00981A(30,000)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>00403A(全數賣出)</t>
+          <t>00993A(-6,000)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00990A(新納入)、00993A(10,000)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>00993A(219,000)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>00403A(全數賣出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>8996</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>全部加碼</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>00407A(130,000)、00993A(40,000)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/etf_holdings/2026-09-03_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-03_common_daily_changes_summary.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,7 +469,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00980A(103,105)、00407A(386,644)、00993A(93,191)</t>
+          <t>00980A(103,105)、00985A(111,036)、00407A(386,644)、00993A(93,191)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,12 +511,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -534,19 +534,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>00407A(-1,045,000)、00993A(-62,000)</t>
+          <t>00992A(-30,000)、00993A(-2,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -554,29 +554,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00993A(85,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>00981A(-1,238,000)</t>
+          <t>00407A(-1,045,000)、00993A(-62,000)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -584,29 +584,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00990A(657,000)、00993A(72,000)</t>
+          <t>00993A(85,000)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00981A(-1,238,000)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00407A(25,000)、00993A(12,000)</t>
+          <t>00990A(657,000)、00993A(72,000)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -631,12 +631,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -644,29 +644,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00990A(新納入)</t>
+          <t>00407A(25,000)、00993A(12,000)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>00993A(-27,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -674,29 +674,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00982A(300,000)、00993A(328,000)</t>
+          <t>00990A(新納入)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(-27,000)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -704,29 +704,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>00981A(30,000)</t>
+          <t>00982A(300,000)、00993A(328,000)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>00993A(-6,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -734,29 +734,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>00990A(新納入)、00993A(10,000)</t>
+          <t>00981A(30,000)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00993A(-6,000)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -764,17 +764,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>00993A(219,000)</t>
+          <t>00990A(新納入)、00993A(10,000)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>00403A(全數賣出)</t>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-09-03_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-03_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,28 +781,58 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>00993A(219,000)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>00403A(全數賣出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>8996</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>全部加碼</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>00407A(130,000)、00993A(40,000)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
